--- a/data/trans_dic/P39A4_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,31; 96,27</t>
+          <t>91,97; 96,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,8; 97,07</t>
+          <t>93,77; 97,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,42; 96,19</t>
+          <t>93,59; 96,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,0; 95,66</t>
+          <t>91,16; 95,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,93; 94,41</t>
+          <t>89,24; 94,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,89; 94,5</t>
+          <t>91,0; 94,7</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,04; 98,73</t>
+          <t>90,77; 98,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,17; 95,45</t>
+          <t>89,67; 95,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,34; 97,51</t>
+          <t>91,45; 98,09</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,0; 94,53</t>
+          <t>91,21; 94,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,4; 97,09</t>
+          <t>92,56; 97,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,27; 95,72</t>
+          <t>92,46; 95,85</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,96; 92,93</t>
+          <t>84,94; 92,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,68; 92,27</t>
+          <t>60,5; 92,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,19; 91,62</t>
+          <t>66,02; 91,42</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,71; 92,13</t>
+          <t>73,54; 92,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,34; 94,2</t>
+          <t>90,22; 94,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,8; 93,0</t>
+          <t>87,93; 93,21</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,45; 94,71</t>
+          <t>91,5; 94,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,54; 93,83</t>
+          <t>83,5; 93,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,43; 93,53</t>
+          <t>88,2; 93,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>455668; 475174</t>
+          <t>453953; 474148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>411275; 425575</t>
+          <t>411104; 425771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>870758; 896506</t>
+          <t>872288; 896222</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>402898; 423509</t>
+          <t>403599; 423362</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>325738; 345814</t>
+          <t>326867; 346550</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>735290; 764486</t>
+          <t>736186; 766166</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>590410; 640322</t>
+          <t>588678; 637084</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>142423; 152450</t>
+          <t>143223; 152968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>738283; 788114</t>
+          <t>739127; 792803</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>878940; 913014</t>
+          <t>880906; 912899</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>874815; 919213</t>
+          <t>876339; 921064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1764729; 1830623</t>
+          <t>1768308; 1833151</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>348915; 381663</t>
+          <t>348823; 381517</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>431438; 678448</t>
+          <t>444818; 679623</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>792926; 1049945</t>
+          <t>756622; 1047671</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>146294; 185367</t>
+          <t>147960; 185971</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>607067; 633021</t>
+          <t>606271; 633862</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>766670; 812053</t>
+          <t>767744; 813854</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2892258; 2995149</t>
+          <t>2893698; 2992788</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2772185; 3113702</t>
+          <t>2770753; 3111497</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5731040; 6061907</t>
+          <t>5716559; 6060298</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A4_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,97; 96,06</t>
+          <t>92,74; 96,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,77; 97,11</t>
+          <t>93,16; 96,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,59; 96,16</t>
+          <t>93,43; 95,95</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,16; 95,62</t>
+          <t>90,45; 95,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,24; 94,61</t>
+          <t>88,92; 94,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,0; 94,7</t>
+          <t>90,66; 94,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,77; 98,24</t>
+          <t>88,27; 94,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,67; 95,77</t>
+          <t>88,13; 94,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,45; 98,09</t>
+          <t>89,54; 93,91</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,21; 94,52</t>
+          <t>89,5; 93,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,56; 97,29</t>
+          <t>90,75; 94,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,46; 95,85</t>
+          <t>90,76; 93,35</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,94; 92,9</t>
+          <t>86,1; 92,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,5; 92,43</t>
+          <t>89,53; 92,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66,02; 91,42</t>
+          <t>88,99; 92,24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73,54; 92,43</t>
+          <t>76,07; 92,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,22; 94,33</t>
+          <t>89,77; 93,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,93; 93,21</t>
+          <t>88,31; 92,81</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,5; 94,63</t>
+          <t>90,74; 92,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,5; 93,76</t>
+          <t>91,49; 93,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,2; 93,51</t>
+          <t>91,39; 92,76</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>466212</t>
+          <t>508638</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>419523</t>
+          <t>454697</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>885735</t>
+          <t>963335</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>453953; 474148</t>
+          <t>498499; 518064</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>411104; 425771</t>
+          <t>445042; 461518</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>872288; 896222</t>
+          <t>948606; 974191</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>414809</t>
+          <t>441807</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>337769</t>
+          <t>370594</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>752578</t>
+          <t>812401</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>403599; 423362</t>
+          <t>428132; 451506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>326867; 346550</t>
+          <t>359308; 379931</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>736186; 766166</t>
+          <t>795466; 825606</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>616269</t>
+          <t>408452</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>148465</t>
+          <t>164617</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>764734</t>
+          <t>573069</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>588678; 637084</t>
+          <t>393045; 418866</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>143223; 152968</t>
+          <t>157838; 169743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>739127; 792803</t>
+          <t>559088; 586330</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>897516</t>
+          <t>965697</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>895148</t>
+          <t>761253</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1792663</t>
+          <t>1726950</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>880906; 912899</t>
+          <t>941694; 983949</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>876339; 921064</t>
+          <t>746269; 773309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1768308; 1833151</t>
+          <t>1701309; 1749818</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>369209</t>
+          <t>421723</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>610887</t>
+          <t>676343</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>980096</t>
+          <t>1098066</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>348823; 381517</t>
+          <t>403819; 434220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>444818; 679623</t>
+          <t>664010; 688659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>756622; 1047671</t>
+          <t>1077324; 1116670</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>171351</t>
+          <t>167964</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>621766</t>
+          <t>682560</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>793117</t>
+          <t>850522</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>147960; 185971</t>
+          <t>147611; 179612</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>606271; 633862</t>
+          <t>665945; 696075</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>767744; 813854</t>
+          <t>826465; 868587</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2935366</t>
+          <t>2914280</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3033557</t>
+          <t>3110062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5968923</t>
+          <t>6024343</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2893698; 2992788</t>
+          <t>2877779; 2946558</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2770753; 3111497</t>
+          <t>3080066; 3135314</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5716559; 6060298</t>
+          <t>5975220; 6065014</t>
         </is>
       </c>
     </row>
